--- a/output/交付物/中国人形机器人产业链研究_数据来源清单.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_数据来源清单.xlsx
@@ -111,10 +111,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
